--- a/site/downloads/files/briefings/cvd_los_2023_v1/workbook/bnr_cvd_los_2023_v1.xlsx
+++ b/site/downloads/files/briefings/cvd_los_2023_v1/workbook/bnr_cvd_los_2023_v1.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="376" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="382" uniqueCount="118">
   <si>
     <t>field</t>
   </si>
@@ -30,10 +30,13 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Target year</t>
-  </si>
-  <si>
-    <t>Baseline period</t>
+    <t>Output type</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>Surveillance area</t>
   </si>
   <si>
     <t>Registry</t>
@@ -42,6 +45,12 @@
     <t>Geography</t>
   </si>
   <si>
+    <t>Period</t>
+  </si>
+  <si>
+    <t>Release date</t>
+  </si>
+  <si>
     <t>Contents</t>
   </si>
   <si>
@@ -57,28 +66,37 @@
     <t>cvd_los_2023_v1</t>
   </si>
   <si>
-    <t>Hospital cardiovascular length of stay in Barbados, 2023</t>
+    <t>Barbados CVD length of stay, 2010-2023</t>
+  </si>
+  <si>
+    <t>briefing</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>CVD</t>
+  </si>
+  <si>
+    <t>BNR-CVD</t>
+  </si>
+  <si>
+    <t>Barbados</t>
   </si>
   <si>
     <t>2023</t>
   </si>
   <si>
-    <t>2010-2021</t>
-  </si>
-  <si>
-    <t>BNR-CVD</t>
-  </si>
-  <si>
-    <t>Barbados</t>
+    <t>2026-05-15</t>
   </si>
   <si>
     <t>Data sheets, dataset metadata sheets, and variable metadata sheets</t>
   </si>
   <si>
-    <t>Aggregate hospital-ascertained length of stay</t>
-  </si>
-  <si>
-    <t>length of stay based on hospital cases</t>
+    <t>Aggregate hospital-ascertained length-of-stay and bed-day demand outputs.</t>
+  </si>
+  <si>
+    <t>Length of stay is based on hospital-ascertained CVD events only.</t>
   </si>
   <si>
     <t>indicator</t>
@@ -400,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -408,7 +426,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
@@ -416,7 +434,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -424,7 +442,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -432,7 +450,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -440,7 +458,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -448,7 +466,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -456,7 +474,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -464,7 +482,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -472,7 +490,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -480,7 +498,31 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -494,34 +536,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
@@ -529,13 +571,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E2" s="1">
         <v>6</v>
@@ -561,13 +603,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E3" s="1">
         <v>6</v>
@@ -593,13 +635,13 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E4" s="1">
         <v>7</v>
@@ -625,13 +667,13 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E5" s="1">
         <v>6</v>
@@ -657,13 +699,13 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
@@ -689,13 +731,13 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E7" s="1">
         <v>7</v>
@@ -721,13 +763,13 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
@@ -753,13 +795,13 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
@@ -785,13 +827,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E10" s="1">
         <v>8</v>
@@ -817,13 +859,13 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E11" s="1">
         <v>7</v>
@@ -849,13 +891,13 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E12" s="1">
         <v>10</v>
@@ -881,13 +923,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
@@ -913,13 +955,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
@@ -945,13 +987,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E15" s="1">
         <v>5</v>
@@ -977,13 +1019,13 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
@@ -1009,13 +1051,13 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
@@ -1041,13 +1083,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E18" s="1">
         <v>6</v>
@@ -1073,13 +1115,13 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E19" s="1">
         <v>6</v>
@@ -1111,200 +1153,200 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1318,255 +1360,255 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G4" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F5" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G5" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F6" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s">
         <v>44</v>
       </c>
-      <c r="B7" t="s">
-        <v>38</v>
-      </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F7" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G7" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F8" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G8" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F9" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G9" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F10" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G10" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F11" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G11" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1580,34 +1622,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2">
@@ -1615,7 +1657,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1">
         <v>2014</v>
@@ -1647,7 +1689,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C3" s="1">
         <v>2015</v>
@@ -1679,7 +1721,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1">
         <v>2016</v>
@@ -1711,7 +1753,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C5" s="1">
         <v>2017</v>
@@ -1743,7 +1785,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1">
         <v>2018</v>
@@ -1775,7 +1817,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C7" s="1">
         <v>2019</v>
@@ -1807,7 +1849,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C8" s="1">
         <v>2020</v>
@@ -1839,7 +1881,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C9" s="1">
         <v>2021</v>
@@ -1871,7 +1913,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1">
         <v>2022</v>
@@ -1903,7 +1945,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1">
         <v>2023</v>
@@ -1935,7 +1977,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1">
         <v>2014</v>
@@ -1967,7 +2009,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1">
         <v>2015</v>
@@ -1999,7 +2041,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1">
         <v>2016</v>
@@ -2031,7 +2073,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C15" s="1">
         <v>2017</v>
@@ -2063,7 +2105,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C16" s="1">
         <v>2018</v>
@@ -2095,7 +2137,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C17" s="1">
         <v>2019</v>
@@ -2127,7 +2169,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C18" s="1">
         <v>2020</v>
@@ -2159,7 +2201,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C19" s="1">
         <v>2021</v>
@@ -2191,7 +2233,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C20" s="1">
         <v>2022</v>
@@ -2223,7 +2265,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C21" s="1">
         <v>2023</v>
@@ -2261,200 +2303,200 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2468,255 +2510,255 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G5" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F6" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F7" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G7" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F8" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G8" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G9" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F10" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G10" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B11" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G11" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/site/downloads/files/briefings/cvd_los_2023_v1/workbook/bnr_cvd_los_2023_v1.xlsx
+++ b/site/downloads/files/briefings/cvd_los_2023_v1/workbook/bnr_cvd_los_2023_v1.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="382" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="382" uniqueCount="121">
   <si>
     <t>field</t>
   </si>
@@ -87,7 +87,7 @@
     <t>2023</t>
   </si>
   <si>
-    <t>2026-05-15</t>
+    <t>2026-08-07</t>
   </si>
   <si>
     <t>Data sheets, dataset metadata sheets, and variable metadata sheets</t>
@@ -231,9 +231,6 @@
     <t>v1</t>
   </si>
   <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
     <t>Ian Hambleton, Analyst</t>
   </si>
   <si>
@@ -264,7 +261,7 @@
     <t>CC BY 4.0 Attribution</t>
   </si>
   <si>
-    <t>Barbados National Registry approved cardiovascular registry extract (Jan 2010-Dec 2023)</t>
+    <t>bnr_cvd_input_length_of_stay_202401_v01; complete calendar years 2010-2023</t>
   </si>
   <si>
     <t>Barbados National Registry</t>
@@ -279,6 +276,12 @@
     <t>float</t>
   </si>
   <si>
+    <t>byte</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>long</t>
   </si>
   <si>
@@ -309,64 +312,70 @@
     <t>variable_label</t>
   </si>
   <si>
-    <t>unique summary measure indicator</t>
-  </si>
-  <si>
-    <t>female=1, male=2, both=3</t>
+    <t>Unique summary measure indicator</t>
+  </si>
+  <si>
+    <t>Female=1, male=2, both=3</t>
   </si>
   <si>
     <t>CVD event type (stroke=1, AMI=2)</t>
   </si>
   <si>
+    <t>CVD event year (2-year intervals)</t>
+  </si>
+  <si>
+    <t>Length of hospital stay: 50th percentile</t>
+  </si>
+  <si>
+    <t>Length of hospital stay: 25th percentile</t>
+  </si>
+  <si>
+    <t>Length of hospital stay: 75th percentile</t>
+  </si>
+  <si>
+    <t>Length of hospital stay: 5th percentile</t>
+  </si>
+  <si>
+    <t>Length of hospital stay: 95th percentile</t>
+  </si>
+  <si>
+    <t>Number of events</t>
+  </si>
+  <si>
+    <t>categories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1=Female; 2=Male; 3=Both; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1=Stroke; 2=AMI; 3=Both; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0=All years; 1=2010-2011; 2=2012-2013; 3=2014-2015; 4=2016-2017; 5=2018-2019; 6=2020-2021; 7=2022-2023; </t>
+  </si>
+  <si>
+    <t>yoe</t>
+  </si>
+  <si>
+    <t>exdays</t>
+  </si>
+  <si>
+    <t>cvd_los_bed_demand</t>
+  </si>
+  <si>
+    <t>BNR-CVD Extra typical bed days (Aggregated)</t>
+  </si>
+  <si>
+    <t>Annual typical bed-days (based on median stay in days)</t>
+  </si>
+  <si>
+    <t>2014-2023</t>
+  </si>
+  <si>
+    <t>Annual typical bed days, based on median length of stay in days.</t>
+  </si>
+  <si>
     <t>CVD event year (yyyy)</t>
-  </si>
-  <si>
-    <t>Length of hospital stay: 50th percentile</t>
-  </si>
-  <si>
-    <t>Length of hospital stay: 25th percentile</t>
-  </si>
-  <si>
-    <t>Length of hospital stay: 75th percentile</t>
-  </si>
-  <si>
-    <t>Length of hospital stay: 5th percentile</t>
-  </si>
-  <si>
-    <t>Length of hospital stay: 95th percentile</t>
-  </si>
-  <si>
-    <t>Number of events</t>
-  </si>
-  <si>
-    <t>categories</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1=Female; 2=Male; 3=Both; </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1=Stroke; 2=AMI; 3=Both; </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0=All years; 1=2010-2011; 2=2012-2013; 3=2014-2015; 4=2016-2017; 5=2018-2019; 6=2020-2021; 7=2022-2023; </t>
-  </si>
-  <si>
-    <t>yoe</t>
-  </si>
-  <si>
-    <t>exdays</t>
-  </si>
-  <si>
-    <t>cvd_los_bed_demand</t>
-  </si>
-  <si>
-    <t>BNR-CVD Extra typical bed days (Aggregated)</t>
-  </si>
-  <si>
-    <t>Annual typical bed-days (based on median stay in days)</t>
-  </si>
-  <si>
-    <t>Annual typical bed days, based on median length of stay in days.</t>
   </si>
   <si>
     <t>Extra typical bed-days per year compared to 2014</t>
@@ -1192,7 +1201,7 @@
         <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -1203,7 +1212,7 @@
         <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -1225,7 +1234,7 @@
         <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8">
@@ -1236,7 +1245,7 @@
         <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
@@ -1247,7 +1256,7 @@
         <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
@@ -1269,7 +1278,7 @@
         <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12">
@@ -1280,7 +1289,7 @@
         <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
@@ -1291,7 +1300,7 @@
         <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14">
@@ -1302,7 +1311,7 @@
         <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1313,7 +1322,7 @@
         <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -1324,7 +1333,7 @@
         <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
@@ -1335,7 +1344,7 @@
         <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -1346,7 +1355,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1363,22 +1372,22 @@
         <v>49</v>
       </c>
       <c r="B1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" t="s">
         <v>83</v>
       </c>
-      <c r="C1" t="s">
-        <v>84</v>
-      </c>
       <c r="D1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2">
@@ -1389,19 +1398,19 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3">
@@ -1415,16 +1424,16 @@
         <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4">
@@ -1438,16 +1447,16 @@
         <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5">
@@ -1458,19 +1467,19 @@
         <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6">
@@ -1481,19 +1490,19 @@
         <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7">
@@ -1504,19 +1513,19 @@
         <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8">
@@ -1527,19 +1536,19 @@
         <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9">
@@ -1550,19 +1559,19 @@
         <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
@@ -1573,19 +1582,19 @@
         <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -1596,19 +1605,19 @@
         <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1628,7 +1637,7 @@
         <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D1" t="s">
         <v>43</v>
@@ -1649,7 +1658,7 @@
         <v>48</v>
       </c>
       <c r="J1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2">
@@ -2314,18 +2323,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B2" t="s">
         <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
@@ -2336,29 +2345,29 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -2369,40 +2378,40 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s">
         <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B10" t="s">
         <v>59</v>
@@ -2413,90 +2422,90 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s">
         <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s">
         <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B13" t="s">
         <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B14" t="s">
         <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B15" t="s">
         <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B16" t="s">
         <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B17" t="s">
         <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B18" t="s">
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2513,50 +2522,50 @@
         <v>49</v>
       </c>
       <c r="B1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" t="s">
         <v>83</v>
       </c>
-      <c r="C1" t="s">
-        <v>84</v>
-      </c>
       <c r="D1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
@@ -2565,200 +2574,200 @@
         <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F4" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="G4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B5" t="s">
         <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s">
         <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s">
         <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B8" t="s">
         <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s">
         <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B10" t="s">
         <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" t="s">
         <v>112</v>
       </c>
-      <c r="B11" t="s">
-        <v>111</v>
-      </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/site/downloads/files/briefings/cvd_los_2023_v1/workbook/bnr_cvd_los_2023_v1.xlsx
+++ b/site/downloads/files/briefings/cvd_los_2023_v1/workbook/bnr_cvd_los_2023_v1.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="382" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="382" uniqueCount="123">
   <si>
     <t>field</t>
   </si>
@@ -87,7 +87,7 @@
     <t>2023</t>
   </si>
   <si>
-    <t>2026-08-07</t>
+    <t>2026-08-13</t>
   </si>
   <si>
     <t>Data sheets, dataset metadata sheets, and variable metadata sheets</t>
@@ -96,7 +96,7 @@
     <t>Aggregate hospital-ascertained length-of-stay and bed-day demand outputs.</t>
   </si>
   <si>
-    <t>Length of stay is based on hospital-ascertained CVD events only.</t>
+    <t>Length of stay is based on hospital-ascertained CVD events with valid admission and end dates. Recorded and inferred in-hospital deaths are included.</t>
   </si>
   <si>
     <t>indicator</t>
@@ -246,10 +246,10 @@
     <t>Event type by period</t>
   </si>
   <si>
-    <t>Annual median length of stay in days.</t>
-  </si>
-  <si>
-    <t>Based on hospital CVD events</t>
+    <t>Annual median length of stay in days, including eligible hospital deaths.</t>
+  </si>
+  <si>
+    <t>Based on hospital CVD events with valid admission and end dates; same-day stays count as one day.</t>
   </si>
   <si>
     <t>en</t>
@@ -282,6 +282,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>double</t>
+  </si>
+  <si>
     <t>long</t>
   </si>
   <si>
@@ -294,6 +297,9 @@
     <t>%8.0g</t>
   </si>
   <si>
+    <t>%10.0g</t>
+  </si>
+  <si>
     <t>value_label</t>
   </si>
   <si>
@@ -366,7 +372,7 @@
     <t>BNR-CVD Extra typical bed days (Aggregated)</t>
   </si>
   <si>
-    <t>Annual typical bed-days (based on median stay in days)</t>
+    <t>Annual typical bed-days based on median stay in days, including eligible hospital deaths.</t>
   </si>
   <si>
     <t>2014-2023</t>
@@ -595,16 +601,16 @@
         <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
       </c>
       <c r="I2" s="1">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J2" s="1">
-        <v>3401</v>
+        <v>4898</v>
       </c>
     </row>
     <row r="3">
@@ -624,19 +630,19 @@
         <v>6</v>
       </c>
       <c r="F3" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3" s="1">
         <v>1</v>
       </c>
       <c r="I3" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J3" s="1">
-        <v>3660</v>
+        <v>4976</v>
       </c>
     </row>
     <row r="4">
@@ -659,16 +665,16 @@
         <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="1">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J4" s="1">
-        <v>4809</v>
+        <v>7065</v>
       </c>
     </row>
     <row r="5">
@@ -688,19 +694,19 @@
         <v>6</v>
       </c>
       <c r="F5" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
         <v>9</v>
       </c>
       <c r="H5" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" s="1">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J5" s="1">
-        <v>2252</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="6">
@@ -717,7 +723,7 @@
         <v>36</v>
       </c>
       <c r="E6" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -726,13 +732,13 @@
         <v>11</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="1">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J6" s="1">
-        <v>551</v>
+        <v>780</v>
       </c>
     </row>
     <row r="7">
@@ -755,16 +761,16 @@
         <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J7" s="1">
-        <v>631</v>
+        <v>929</v>
       </c>
     </row>
     <row r="8">
@@ -790,13 +796,13 @@
         <v>14</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="1">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="J8" s="1">
-        <v>673</v>
+        <v>951</v>
       </c>
     </row>
     <row r="9">
@@ -816,19 +822,19 @@
         <v>6</v>
       </c>
       <c r="F9" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
         <v>15</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="1">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J9" s="1">
-        <v>735</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="10">
@@ -845,22 +851,22 @@
         <v>40</v>
       </c>
       <c r="E10" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" s="1">
         <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
       </c>
       <c r="I10" s="1">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J10" s="1">
-        <v>786</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="11">
@@ -883,16 +889,16 @@
         <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H11" s="1">
         <v>1</v>
       </c>
       <c r="I11" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J11" s="1">
-        <v>733</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="12">
@@ -909,22 +915,22 @@
         <v>42</v>
       </c>
       <c r="E12" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
       </c>
       <c r="I12" s="1">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J12" s="1">
-        <v>700</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="13">
@@ -953,10 +959,10 @@
         <v>3</v>
       </c>
       <c r="I13" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J13" s="1">
-        <v>192</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14">
@@ -985,10 +991,10 @@
         <v>3</v>
       </c>
       <c r="I14" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J14" s="1">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15">
@@ -1017,10 +1023,10 @@
         <v>3</v>
       </c>
       <c r="I15" s="1">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J15" s="1">
-        <v>326</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16">
@@ -1046,13 +1052,13 @@
         <v>9</v>
       </c>
       <c r="H16" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" s="1">
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="J16" s="1">
-        <v>400</v>
+        <v>496</v>
       </c>
     </row>
     <row r="17">
@@ -1072,19 +1078,19 @@
         <v>6</v>
       </c>
       <c r="F17" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G17" s="1">
         <v>9</v>
       </c>
       <c r="H17" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I17" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J17" s="1">
-        <v>428</v>
+        <v>568</v>
       </c>
     </row>
     <row r="18">
@@ -1101,22 +1107,22 @@
         <v>41</v>
       </c>
       <c r="E18" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
         <v>8</v>
       </c>
       <c r="H18" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I18" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J18" s="1">
-        <v>345</v>
+        <v>481</v>
       </c>
     </row>
     <row r="19">
@@ -1136,19 +1142,19 @@
         <v>6</v>
       </c>
       <c r="F19" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
         <v>9</v>
       </c>
       <c r="H19" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J19" s="1">
-        <v>290</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>
@@ -1378,16 +1384,16 @@
         <v>83</v>
       </c>
       <c r="D1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2">
@@ -1401,16 +1407,16 @@
         <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3">
@@ -1424,16 +1430,16 @@
         <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4">
@@ -1447,16 +1453,16 @@
         <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5">
@@ -1470,16 +1476,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6">
@@ -1490,19 +1496,19 @@
         <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7">
@@ -1513,19 +1519,19 @@
         <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8">
@@ -1536,19 +1542,19 @@
         <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9">
@@ -1559,19 +1565,19 @@
         <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
@@ -1582,19 +1588,19 @@
         <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -1605,19 +1611,19 @@
         <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1637,7 +1643,7 @@
         <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D1" t="s">
         <v>43</v>
@@ -1658,7 +1664,7 @@
         <v>48</v>
       </c>
       <c r="J1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2">
@@ -1678,16 +1684,16 @@
         <v>2</v>
       </c>
       <c r="F2" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="1">
         <v>1</v>
       </c>
       <c r="H2" s="1">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I2" s="1">
-        <v>347</v>
+        <v>476</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
@@ -1704,25 +1710,25 @@
         <v>2015</v>
       </c>
       <c r="D3" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" s="1">
         <v>2</v>
       </c>
       <c r="F3" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" s="1">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1">
+        <v>46</v>
+      </c>
+      <c r="I3" s="1">
+        <v>474</v>
+      </c>
+      <c r="J3" s="1">
         <v>0</v>
-      </c>
-      <c r="H3" s="1">
-        <v>35</v>
-      </c>
-      <c r="I3" s="1">
-        <v>326</v>
-      </c>
-      <c r="J3" s="1">
-        <v>-326</v>
       </c>
     </row>
     <row r="4">
@@ -1736,25 +1742,25 @@
         <v>2016</v>
       </c>
       <c r="D4" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1">
+        <v>42.5</v>
+      </c>
+      <c r="I4" s="1">
+        <v>560</v>
+      </c>
+      <c r="J4" s="1">
         <v>0</v>
-      </c>
-      <c r="H4" s="1">
-        <v>32</v>
-      </c>
-      <c r="I4" s="1">
-        <v>362</v>
-      </c>
-      <c r="J4" s="1">
-        <v>-362</v>
       </c>
     </row>
     <row r="5">
@@ -1768,25 +1774,25 @@
         <v>2017</v>
       </c>
       <c r="D5" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="1">
         <v>2</v>
       </c>
       <c r="F5" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="1">
         <v>47</v>
       </c>
       <c r="I5" s="1">
-        <v>373</v>
+        <v>542</v>
       </c>
       <c r="J5" s="1">
-        <v>373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1812,13 +1818,13 @@
         <v>1</v>
       </c>
       <c r="H6" s="1">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I6" s="1">
-        <v>397</v>
+        <v>548</v>
       </c>
       <c r="J6" s="1">
-        <v>397</v>
+        <v>548</v>
       </c>
     </row>
     <row r="7">
@@ -1832,25 +1838,25 @@
         <v>2019</v>
       </c>
       <c r="D7" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
       </c>
       <c r="H7" s="1">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I7" s="1">
-        <v>389</v>
+        <v>617</v>
       </c>
       <c r="J7" s="1">
-        <v>1167</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="8">
@@ -1867,22 +1873,22 @@
         <v>7</v>
       </c>
       <c r="E8" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
       </c>
       <c r="H8" s="1">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I8" s="1">
-        <v>385</v>
+        <v>562</v>
       </c>
       <c r="J8" s="1">
-        <v>385</v>
+        <v>562</v>
       </c>
     </row>
     <row r="9">
@@ -1902,7 +1908,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -1911,10 +1917,10 @@
         <v>47</v>
       </c>
       <c r="I9" s="1">
-        <v>349</v>
+        <v>505</v>
       </c>
       <c r="J9" s="1">
-        <v>698</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="10">
@@ -1928,13 +1934,13 @@
         <v>2022</v>
       </c>
       <c r="D10" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
       </c>
       <c r="F10" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1943,10 +1949,10 @@
         <v>46</v>
       </c>
       <c r="I10" s="1">
-        <v>356</v>
+        <v>518</v>
       </c>
       <c r="J10" s="1">
-        <v>1424</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="11">
@@ -1960,25 +1966,25 @@
         <v>2023</v>
       </c>
       <c r="D11" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
       </c>
       <c r="H11" s="1">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I11" s="1">
-        <v>343</v>
+        <v>553</v>
       </c>
       <c r="J11" s="1">
-        <v>1372</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="12">
@@ -1998,16 +2004,16 @@
         <v>4</v>
       </c>
       <c r="F12" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
         <v>3</v>
       </c>
       <c r="H12" s="1">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="I12" s="1">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J12" s="1">
         <v>0</v>
@@ -2036,13 +2042,13 @@
         <v>3</v>
       </c>
       <c r="H13" s="1">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I13" s="1">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J13" s="1">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14">
@@ -2059,22 +2065,22 @@
         <v>6</v>
       </c>
       <c r="E14" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1">
         <v>8</v>
       </c>
       <c r="G14" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H14" s="1">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I14" s="1">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="J14" s="1">
-        <v>179</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15">
@@ -2097,16 +2103,16 @@
         <v>10</v>
       </c>
       <c r="G15" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H15" s="1">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I15" s="1">
-        <v>221</v>
+        <v>278</v>
       </c>
       <c r="J15" s="1">
-        <v>221</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16">
@@ -2123,22 +2129,22 @@
         <v>6</v>
       </c>
       <c r="E16" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1">
         <v>9</v>
       </c>
       <c r="G16" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" s="1">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I16" s="1">
-        <v>194</v>
+        <v>257</v>
       </c>
       <c r="J16" s="1">
-        <v>194</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17">
@@ -2161,16 +2167,16 @@
         <v>9</v>
       </c>
       <c r="G17" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" s="1">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I17" s="1">
-        <v>234</v>
+        <v>311</v>
       </c>
       <c r="J17" s="1">
-        <v>234</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18">
@@ -2184,25 +2190,25 @@
         <v>2020</v>
       </c>
       <c r="D18" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F18" s="1">
         <v>8</v>
       </c>
       <c r="G18" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" s="1">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I18" s="1">
-        <v>222</v>
+        <v>290</v>
       </c>
       <c r="J18" s="1">
-        <v>222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2216,25 +2222,25 @@
         <v>2021</v>
       </c>
       <c r="D19" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F19" s="1">
         <v>8</v>
       </c>
       <c r="G19" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I19" s="1">
-        <v>123</v>
+        <v>192</v>
       </c>
       <c r="J19" s="1">
-        <v>123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2251,22 +2257,22 @@
         <v>6</v>
       </c>
       <c r="E20" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F20" s="1">
         <v>9</v>
       </c>
       <c r="G20" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20" s="1">
         <v>22</v>
       </c>
       <c r="I20" s="1">
-        <v>134</v>
+        <v>215</v>
       </c>
       <c r="J20" s="1">
-        <v>134</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21">
@@ -2280,25 +2286,25 @@
         <v>2023</v>
       </c>
       <c r="D21" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1">
         <v>9</v>
       </c>
       <c r="G21" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21" s="1">
         <v>15</v>
       </c>
       <c r="I21" s="1">
-        <v>156</v>
+        <v>230</v>
       </c>
       <c r="J21" s="1">
-        <v>312</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -2323,18 +2329,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B2" t="s">
         <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
@@ -2345,7 +2351,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
@@ -2356,7 +2362,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -2367,7 +2373,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -2378,18 +2384,18 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
@@ -2400,18 +2406,18 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B9" t="s">
         <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s">
         <v>59</v>
@@ -2422,7 +2428,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B11" t="s">
         <v>60</v>
@@ -2433,18 +2439,18 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B12" t="s">
         <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B13" t="s">
         <v>62</v>
@@ -2455,7 +2461,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B14" t="s">
         <v>63</v>
@@ -2466,7 +2472,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B15" t="s">
         <v>64</v>
@@ -2477,7 +2483,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B16" t="s">
         <v>65</v>
@@ -2488,7 +2494,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B17" t="s">
         <v>66</v>
@@ -2499,7 +2505,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B18" t="s">
         <v>67</v>
@@ -2528,21 +2534,21 @@
         <v>83</v>
       </c>
       <c r="D1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
@@ -2551,21 +2557,21 @@
         <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
@@ -2574,200 +2580,200 @@
         <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
         <v>113</v>
-      </c>
-      <c r="B4" t="s">
-        <v>111</v>
       </c>
       <c r="C4" t="s">
         <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B5" t="s">
         <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B6" t="s">
         <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s">
         <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B8" t="s">
         <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B9" t="s">
         <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s">
         <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C11" t="s">
         <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
